--- a/logs/experiments_not_systematic/combining_results/experiments_summary.xlsx
+++ b/logs/experiments_not_systematic/combining_results/experiments_summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/combining_results/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/experiments_not_systematic/combining_results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="91" documentId="11_6F1971BED38051FDBCC901D04B5ED87656CC73B7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3256D6E-669A-4115-A942-64D471C33285}"/>
+  <xr:revisionPtr revIDLastSave="95" documentId="11_6F1971BED38051FDBCC901D04B5ED87656CC73B7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCDE0241-2A26-4EA1-8712-762CCE801641}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,13 +18,13 @@
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="124">
   <si>
     <t>date</t>
   </si>
@@ -1729,8 +1729,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A35AA65C-496D-40E9-88FB-E84AC916F44B}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:I9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A35AA65C-496D-40E9-88FB-E84AC916F44B}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:I11" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="76">
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
@@ -1774,8 +1774,8 @@
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="4">
-        <item sd="0" x="1"/>
-        <item sd="0" x="0"/>
+        <item x="1"/>
+        <item x="0"/>
         <item x="2"/>
         <item t="default"/>
       </items>
@@ -1839,12 +1839,18 @@
     <field x="19"/>
     <field x="2"/>
   </rowFields>
-  <rowItems count="6">
+  <rowItems count="8">
     <i>
       <x/>
     </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
     <i>
       <x v="1"/>
+    </i>
+    <i r="1">
+      <x/>
     </i>
     <i>
       <x v="2"/>
@@ -1899,7 +1905,7 @@
     <dataField name="Cuenta de model_id" fld="1" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <conditionalFormats count="2">
-    <conditionalFormat priority="2">
+    <conditionalFormat priority="1">
       <pivotAreas count="1">
         <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="1">
@@ -1916,7 +1922,7 @@
         </pivotArea>
       </pivotAreas>
     </conditionalFormat>
-    <conditionalFormat priority="1">
+    <conditionalFormat priority="2">
       <pivotAreas count="1">
         <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="1">
@@ -5349,7 +5355,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{439A399D-98B1-49AF-B389-8AFC2449F128}">
-  <dimension ref="A3:I9"/>
+  <dimension ref="A3:I11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -5422,29 +5428,29 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>89</v>
+      <c r="A5" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="B5" s="6">
-        <v>0.82282938921006721</v>
+        <v>0.90241694667057215</v>
       </c>
       <c r="C5" s="6">
-        <v>-1.3687998659942509</v>
+        <v>-0.156779683615695</v>
       </c>
       <c r="D5" s="6">
-        <v>0.82678211814889557</v>
+        <v>0.90830229393002904</v>
       </c>
       <c r="E5" s="6">
-        <v>0.90693888560350688</v>
+        <v>0.91454012106688098</v>
       </c>
       <c r="F5" s="6">
-        <v>0.62493869508849231</v>
+        <v>0.94254600898978991</v>
       </c>
       <c r="G5" s="6">
-        <v>0.9206063692910762</v>
+        <v>0.91556934269351087</v>
       </c>
       <c r="H5" s="6">
-        <v>0.85464452261250512</v>
+        <v>0.8605537029699345</v>
       </c>
       <c r="I5" s="6">
         <v>3</v>
@@ -5452,31 +5458,31 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="B6" s="6">
-        <v>0.71415814342101169</v>
+        <v>0.82282938921006721</v>
       </c>
       <c r="C6" s="6">
-        <v>-5.1585405425586615E-2</v>
+        <v>-1.3687998659942509</v>
       </c>
       <c r="D6" s="6">
-        <v>0.71130995985360634</v>
+        <v>0.82678211814889557</v>
       </c>
       <c r="E6" s="6">
-        <v>0.91928639235122767</v>
+        <v>0.90693888560350688</v>
       </c>
       <c r="F6" s="6">
-        <v>0.17401032110759826</v>
+        <v>0.62493869508849231</v>
       </c>
       <c r="G6" s="6">
-        <v>0.91745311388480333</v>
+        <v>0.9206063692910762</v>
       </c>
       <c r="H6" s="6">
-        <v>0.83449001207079354</v>
+        <v>0.85464452261250512</v>
       </c>
       <c r="I6" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -5484,90 +5490,148 @@
         <v>87</v>
       </c>
       <c r="B7" s="6">
-        <v>0.69277013292935141</v>
+        <v>0.82282938921006721</v>
       </c>
       <c r="C7" s="6">
-        <v>-2.9909017637599195E-2</v>
+        <v>-1.3687998659942509</v>
       </c>
       <c r="D7" s="6">
-        <v>0.68967992713824422</v>
+        <v>0.82678211814889557</v>
       </c>
       <c r="E7" s="6">
-        <v>0.92259008083901717</v>
+        <v>0.90693888560350688</v>
       </c>
       <c r="F7" s="6">
-        <v>0.11687196208004451</v>
+        <v>0.62493869508849231</v>
       </c>
       <c r="G7" s="6">
-        <v>0.90096711193343337</v>
+        <v>0.9206063692910762</v>
       </c>
       <c r="H7" s="6">
-        <v>0.81829055370047821</v>
+        <v>0.85464452261250512</v>
       </c>
       <c r="I7" s="6">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>99</v>
+      <c r="A8" s="4" t="s">
+        <v>106</v>
       </c>
       <c r="B8" s="6">
-        <v>0.73554615391267186</v>
+        <v>0.71415814342101169</v>
       </c>
       <c r="C8" s="6">
-        <v>-7.3261793213574039E-2</v>
+        <v>-5.1585405425586615E-2</v>
       </c>
       <c r="D8" s="6">
-        <v>0.73293999256896836</v>
+        <v>0.71130995985360634</v>
       </c>
       <c r="E8" s="6">
-        <v>0.91598270386343827</v>
+        <v>0.91928639235122767</v>
       </c>
       <c r="F8" s="6">
-        <v>0.23114868013515197</v>
+        <v>0.17401032110759826</v>
       </c>
       <c r="G8" s="6">
-        <v>0.93393911583617284</v>
+        <v>0.91745311388480333</v>
       </c>
       <c r="H8" s="6">
-        <v>0.85068947044110887</v>
+        <v>0.83449001207079354</v>
       </c>
       <c r="I8" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" s="6">
+        <v>0.69277013292935141</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-2.9909017637599195E-2</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0.68967992713824422</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.92259008083901717</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0.11687196208004451</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0.90096711193343337</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0.81829055370047821</v>
+      </c>
+      <c r="I9" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" s="6">
+        <v>0.73554615391267186</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-7.3261793213574039E-2</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.73293999256896836</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.91598270386343827</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0.23114868013515197</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0.93393911583617284</v>
+      </c>
+      <c r="H10" s="6">
+        <v>0.85068947044110887</v>
+      </c>
+      <c r="I10" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B11" s="6">
         <v>0.78839065568066558</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C11" s="6">
         <v>-0.40718759011527972</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D11" s="6">
         <v>0.78942608294653427</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E11" s="6">
         <v>0.91501294784321086</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F11" s="6">
         <v>0.4788763365733697</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G11" s="6">
         <v>0.9177704849385484</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H11" s="6">
         <v>0.84604456243100667</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I11" s="6">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting pivot="1" sqref="B4:H9">
+  <conditionalFormatting pivot="1" sqref="B4:H11">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -5579,7 +5643,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting pivot="1" sqref="B4:H9">
+  <conditionalFormatting pivot="1" sqref="B4:H11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
